--- a/consent_forms/043_remote_work_consent_form--consent_forms.xlsx
+++ b/consent_forms/043_remote_work_consent_form--consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'full-time_remote',_'value':_'full-time-remote'}</t>
+          <t>full-time-remote</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Full-time Remote', 'value': 'full-time-remote'}</t>
+          <t>full-time-remote</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'part-time_remote',_'value':_'part-time-remote'}</t>
+          <t>part-time-remote</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Part-time Remote', 'value': 'part-time-remote'}</t>
+          <t>part-time-remote</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'remote_work_with_regular_hours',_'value':_'remote-work-with-regular-hours'}</t>
+          <t>remote-work-with-regular-hours</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Remote Work with Regular Hours', 'value': 'remote-work-with-regular-hours'}</t>
+          <t>remote-work-with-regular-hours</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'remote_work_with_flexible_hours',_'value':_'remote-work-with-flexible-hours'}</t>
+          <t>remote-work-with-flexible-hours</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Remote Work with Flexible Hours', 'value': 'remote-work-with-flexible-hours'}</t>
+          <t>remote-work-with-flexible-hours</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'home',_'value':_'home'}</t>
+          <t>home</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Home', 'value': 'home'}</t>
+          <t>home</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'office',_'value':_'office'}</t>
+          <t>office</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Office', 'value': 'office'}</t>
+          <t>office</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'co-working_space',_'value':_'co-working-space'}</t>
+          <t>co-working-space</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Co-working Space', 'value': 'co-working-space'}</t>
+          <t>co-working-space</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Other', 'value': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'manager',_'value':_'manager'}</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Manager', 'value': 'manager'}</t>
+          <t>manager</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'assistant_manager',_'value':_'assistant-manager'}</t>
+          <t>assistant-manager</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Assistant Manager', 'value': 'assistant-manager'}</t>
+          <t>assistant-manager</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'team_lead',_'value':_'team-lead'}</t>
+          <t>team-lead</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Team Lead', 'value': 'team-lead'}</t>
+          <t>team-lead</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'personal_computer',_'value':_'personal-computer'}</t>
+          <t>personal-computer</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Personal Computer', 'value': 'personal-computer'}</t>
+          <t>personal-computer</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'internet_connection',_'value':_'internet-connection'}</t>
+          <t>internet-connection</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Internet Connection', 'value': 'internet-connection'}</t>
+          <t>internet-connection</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'headset',_'value':_'headset'}</t>
+          <t>headset</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Headset', 'value': 'headset'}</t>
+          <t>headset</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Other', 'value': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'agree',_'value':_'agree'}</t>
+          <t>agree</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Agree', 'value': 'agree'}</t>
+          <t>agree</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'disagree',_'value':_'disagree'}</t>
+          <t>disagree</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Disagree', 'value': 'disagree'}</t>
+          <t>disagree</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
